--- a/Estoque/Estoque 06.2026.xlsx
+++ b/Estoque/Estoque 06.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Estoque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A023380-6385-4159-B8DD-4B1E5F642B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F0DAAD-5D0D-4A86-99EA-118645A2950C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8E53B96B-8C82-452A-AAB2-5E3C25B6EC39}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t xml:space="preserve">Fazenda Vera Cruz - Furnas </t>
   </si>
@@ -135,6 +135,12 @@
   </si>
   <si>
     <t>FEMEA RECRIA</t>
+  </si>
+  <si>
+    <t>QTDE</t>
+  </si>
+  <si>
+    <t>CUSTO MÉDIO</t>
   </si>
 </sst>
 </file>
@@ -539,18 +545,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D5A0105-4138-4C1C-8F61-B2C114D92FF9}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -568,7 +578,7 @@
       </c>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -592,7 +602,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -617,7 +627,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -632,7 +642,7 @@
         <v>4149.9876701020776</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -650,7 +660,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -674,7 +684,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -699,7 +709,7 @@
         <v>0.59000000000000008</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -714,7 +724,7 @@
         <v>4648.7207252275648</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -729,7 +739,7 @@
         <v>4116.3740428597084</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -744,7 +754,7 @@
         <v>8498.902033646209</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -758,8 +768,17 @@
       <c r="E11" s="3">
         <v>5439.2956144709387</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -771,12 +790,14 @@
         <v>30</v>
       </c>
       <c r="H12" s="5">
-        <f>61+30871+1546+5319-3-17666-1395-334</f>
         <v>18399</v>
       </c>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I12" s="5">
+        <v>4391.7627481739937</v>
+      </c>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -788,9 +809,26 @@
         <v>31</v>
       </c>
       <c r="H13" s="5">
-        <f>902+412+356+3228-32</f>
         <v>4866</v>
       </c>
+      <c r="I13" s="5">
+        <v>2996.5954727296535</v>
+      </c>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="8:12" x14ac:dyDescent="0.3">
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
